--- a/reports/reconciliation_report.xlsx
+++ b/reports/reconciliation_report.xlsx
@@ -7,7 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Issue Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Severity Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Discrepancies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Only in Source A" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Only in Source B" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,118 +418,496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CUSIP</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Security Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Issue Date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Maturity Date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Coupon Rate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Outstanding Balance</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Market Price</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Exchange</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>456123789</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Source A</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEF Mortgage Backed</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MBS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2035-03-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4.00%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>98.75</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
+          <t>Bloomberg Sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ICE Sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Source A Rows</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Source B Rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Source A Unique CUSIPs</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Source B Unique CUSIPs</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Matched Records</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total Discrepancies</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Field Mismatches</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Only in Source A</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Only in Source B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Source A Duplicate Rows</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Source B Duplicate Rows</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Match Rate (%)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Issue Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Field Mismatch</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cusip</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>security_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>issue_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>field_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_a_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source_b_value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>asset_class</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABC Corp Bond</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Field Mismatch</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Market Price</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Market Price differs between Bloomberg Sample and ICE Sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>456123789</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEF Mortgage Backed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Field Mismatch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Market Price</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>98.75</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MBS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Market Price differs between Bloomberg Sample and ICE Sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>654789123</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GHI Treasury Bond</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Field Mismatch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Outstanding Balance</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>250,000.00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>200,000.00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Outstanding Balance differs between Bloomberg Sample and ICE Sample.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>